--- a/data/mini-example-resilience/Heat_P2H_Technologies.xlsx
+++ b/data/mini-example-resilience/Heat_P2H_Technologies.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\Mini-example-resilience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5A669C-7439-4AE0-BDA1-5458898C6B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5F1B97-C62F-4DD6-B9C3-EDC667241001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -877,13 +877,13 @@
         <v>45</v>
       </c>
       <c r="F8" s="12">
-        <v>40</v>
+        <v>0.8</v>
       </c>
       <c r="G8" s="12">
         <v>1</v>
       </c>
       <c r="H8" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="12">
         <v>0.8</v>

--- a/data/mini-example-resilience/Heat_P2H_Technologies.xlsx
+++ b/data/mini-example-resilience/Heat_P2H_Technologies.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5F1B97-C62F-4DD6-B9C3-EDC667241001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A0BE14-B0E4-4C63-9227-BFA562851BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -886,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="12">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J8" s="12">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="K8" s="12">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
